--- a/outputs/ranker/baseline/learned_objective_weights.xlsx
+++ b/outputs/ranker/baseline/learned_objective_weights.xlsx
@@ -486,10 +486,10 @@
         <v>0.05</v>
       </c>
       <c r="C2">
-        <v>0.2975817440753323</v>
+        <v>0.2976881088847934</v>
       </c>
       <c r="D2">
-        <v>0.1861699592414328</v>
+        <v>0.1862284598866364</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -503,10 +503,10 @@
         <v>0.05</v>
       </c>
       <c r="C3">
-        <v>0.2962545024393946</v>
+        <v>0.2969153065494276</v>
       </c>
       <c r="D3">
-        <v>0.185439976341667</v>
+        <v>0.1858034186021852</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -520,10 +520,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C4">
-        <v>0.2584563960247734</v>
+        <v>0.2422405782993529</v>
       </c>
       <c r="D4">
-        <v>0.1736510178136254</v>
+        <v>0.1647323180646442</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -537,10 +537,10 @@
         <v>0.09</v>
       </c>
       <c r="C5">
-        <v>0.1477073574604995</v>
+        <v>0.1631560062664259</v>
       </c>
       <c r="D5">
-        <v>0.1217390466032748</v>
+        <v>0.1302358034465343</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -557,7 +557,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.09899999999999999</v>
+        <v>0.09900000000000002</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.07199999999999999</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.04049999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -608,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.04049999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="E9" t="s">
         <v>24</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0.0045</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
